--- a/naver-place-crawler/results_health/미추홀구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/미추홀구_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -2623,39 +2623,39 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>수영장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>에이스스포츠센터</t>
+          <t>터닝포인트짐 헬스 PT 주안점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jmsd1104@naver.com</t>
+          <t>tpg21@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>032-422-4420</t>
+          <t>0507-1360-9997</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 434 제일빌딩</t>
+          <t>인천광역시 미추홀구 미추홀대로 730 고려빌딩 4층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jmsd1104</t>
+          <t>https://www.tpgymjooan.com/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2676,22 +2676,22 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>456</v>
+        <v>1145</v>
       </c>
       <c r="Q24" t="n">
-        <v>55</v>
+        <v>1379</v>
       </c>
       <c r="R24" t="n">
-        <v>511</v>
+        <v>2524</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2700,12 +2700,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>31793861</t>
+          <t>1015443504</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31793861</t>
+          <t>https://m.place.naver.com/place/1015443504</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2717,39 +2717,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>어게인핏 PT 주안점</t>
+          <t>인싸짐 주안점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>yeoninmo@naver.com</t>
+          <t>inssagym3@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1394-8036</t>
+          <t>0507-1332-3818</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 구월로40번길 4 2층 어게인핏</t>
+          <t>인천광역시 미추홀구 경원대로 848 지하2층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/again_fit_juan?igsh=cGJremczeG83cTA%3D&amp;utm_source=qr</t>
+          <t>https://m.booking.naver.com/booking/5/bizes/840698?area=pll&amp;service-target=map-pc&amp;theme=place</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2770,7 +2770,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>72</v>
+        <v>1577</v>
       </c>
       <c r="Q25" t="n">
-        <v>125</v>
+        <v>1224</v>
       </c>
       <c r="R25" t="n">
-        <v>197</v>
+        <v>2801</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1470836324</t>
+          <t>1070990223</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1470836324</t>
+          <t>https://m.place.naver.com/place/1070990223</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -2811,34 +2811,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>베럴핏 용현점</t>
+          <t>라이노짐 인천도화점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>betterfitpt@naver.com</t>
+          <t>smhon833@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1401-5990</t>
+          <t>0507-1349-3268</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 63 대신프라자 702호 베럴핏</t>
+          <t>인천광역시 미추홀구 송림로 249 새마을금고 3층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/betterfitpt</t>
+          <t>https://blog.naver.com/smhon833</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2869,17 +2869,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="Q26" t="n">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="R26" t="n">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>37890204</t>
+          <t>1098224618</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37890204</t>
+          <t>https://m.place.naver.com/place/1098224618</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -2905,34 +2905,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>와이키키 트레이닝클럽</t>
+          <t>넘버제로짐 헬스&amp;PT 주안역점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>waikiki_trainingclub@naver.com</t>
+          <t>sid1287@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1489-8101</t>
+          <t>0507-1363-2606</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인하로 87-1 B1</t>
+          <t>인천광역시 미추홀구 미추홀대로 725 5층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/waikiki_trainingclub_inha</t>
+          <t>https://www.instagram.com/no.0pt/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2967,13 +2967,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="Q27" t="n">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="R27" t="n">
-        <v>123</v>
+        <v>846</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2982,12 +2982,12 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1324912852</t>
+          <t>1326633826</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324912852</t>
+          <t>https://m.place.naver.com/place/1326633826</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -2999,34 +2999,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>바름핏 pt&amp;필라테스 주안점</t>
+          <t>에이지트레이닝피티 주안점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>brfpt@naver.com</t>
+          <t>goodleedy@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1490-4455</t>
+          <t>0507-1305-5338</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 370 7층</t>
+          <t>인천광역시 미추홀구 경인로325번길 27 3층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bareumfit/</t>
+          <t>https://www.instagram.com/ag_training_juan/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3061,13 +3061,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1623977840</t>
+          <t>2007007809</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623977840</t>
+          <t>https://m.place.naver.com/place/2007007809</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3093,34 +3093,34 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>광고대행</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PT의품격 용현점</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jaeyounggom@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1445-6077</t>
+          <t>070-4572-4927</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 아암대로45번길 77-8 2층 201호</t>
+          <t>인천광역시 미추홀구 도화동</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jaeyounggom</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>336</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>399</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>735</v>
+        <v>0</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1048465766</t>
+          <t>1127666908</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1048465766</t>
+          <t>https://m.place.naver.com/place/1127666908</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3187,39 +3187,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>바름핏 PT&amp;필라테스 본점</t>
+          <t>제이짐휘트니스 주안점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>brfpt@naver.com</t>
+          <t>csys026@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1455-8691</t>
+          <t>0507-1330-7817</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 소성로 150 2층바름핏</t>
+          <t>인천광역시 미추홀구 길파로 7 주안프라자 7층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/brfpt</t>
+          <t>http://pf.kakao.com/_gxbxkhG/chat</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3240,22 +3240,22 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="Q30" t="n">
-        <v>358</v>
+        <v>25</v>
       </c>
       <c r="R30" t="n">
-        <v>638</v>
+        <v>125</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3264,12 +3264,12 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1493566392</t>
+          <t>1927377740</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1493566392</t>
+          <t>https://m.place.naver.com/place/1927377740</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3281,39 +3281,39 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>레몬짐 용현점</t>
+          <t>바른습관PT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lafcompany_@naver.com</t>
+          <t>hyptjuan@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1373-2249</t>
+          <t>0507-1466-0535</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 311 비젼프라자 11층 레몬짐 용현점</t>
+          <t>인천광역시 미추홀구 염창로 65 4층 바른습관 PT STUDIO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>http://www.lemongym.co.kr</t>
+          <t>https://www.instagram.com/mgm_hypt?igsh=ODA1NTc5OTg5Nw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3334,7 +3334,7 @@
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3343,13 +3343,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>362</v>
+        <v>106</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="R31" t="n">
-        <v>373</v>
+        <v>173</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1984607952</t>
+          <t>1761795724</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1984607952</t>
+          <t>https://m.place.naver.com/place/1761795724</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3375,34 +3375,34 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>뉴케이와이피트니스</t>
+          <t>와이키키짐 PT 주안점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5830666@naver.com</t>
+          <t>waikikigym2311@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0505-720-1633</t>
+          <t>0507-1365-4408</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 510 지하1층</t>
+          <t>인천광역시 미추홀구 미추홀대로 710 지하1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/waikikigym_jwsong?igsh=bG51c2U5anlmZ2Ez&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3433,17 +3433,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1546</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1667</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3452,12 +3452,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>2090228880</t>
+          <t>1085067011</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090228880</t>
+          <t>https://m.place.naver.com/place/1085067011</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3469,34 +3469,34 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>저스트PT짐</t>
+          <t>현헬스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rlaehgus1236@naver.com</t>
+          <t>kingkong-play@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1379-2006</t>
+          <t>032-863-8673</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로317번길 29 11층</t>
+          <t>인천광역시 미추홀구 제일로 48 3층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rlaehgus1236</t>
+          <t>https://blog.naver.com/kingkong-play</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="Q33" t="n">
-        <v>209</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>328</v>
+        <v>22</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3546,12 +3546,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1324594280</t>
+          <t>1145507902</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324594280</t>
+          <t>https://m.place.naver.com/place/1145507902</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3563,39 +3563,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>뉴바디짐</t>
+          <t>팀크루즈 역도체육관&amp;PT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>godanhe@naver.com</t>
+          <t>team_cruise@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>032-710-1633</t>
+          <t>0507-1341-0981</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로317번길 23 해성프라자 6층 뉴바디짐</t>
+          <t>인천광역시 미추홀구 인주대로 438 삼영빌딩 지하1층</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_yyvMxb/chat</t>
+          <t>https://www.instagram.com/teamcruise_juan/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3616,7 +3616,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3625,13 +3625,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="Q34" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="R34" t="n">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3640,12 +3640,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1357445067</t>
+          <t>1455972728</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1357445067</t>
+          <t>https://m.place.naver.com/place/1455972728</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3657,34 +3657,34 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>흐름필라테스&amp;요가</t>
+          <t>포텐휘트니스</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>hrmpilayoga@naver.com</t>
+          <t>jyj09623@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1470-8448</t>
+          <t>0507-1336-2892</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 송림로 251 창조프라자 4층</t>
+          <t>인천광역시 미추홀구 토금중로 13 4층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hrmpilayoga</t>
+          <t>https://linktr.ee/fitness410</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3719,30 +3719,6116 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>155</v>
+      </c>
+      <c r="R35" t="n">
+        <v>276</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1932083996</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1932083996</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>포멀짐 헬스&amp;피티 제물포점</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>formalgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1365-5941</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 128 2층 포멀짐</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/formalgym</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>9</v>
+      </c>
+      <c r="R36" t="n">
+        <v>111</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1933593128</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1933593128</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>하이엔드 휘트니스 주안</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>highendfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1477-3415</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경원대로 869 르네상스타워 19층 하이엔드 휘트니스</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>http://www.highendfitness.kr/</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>522</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>185</v>
+      </c>
+      <c r="R37" t="n">
+        <v>707</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1851949492</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1851949492</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>모먼트짐 학익점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jhmomentgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1340-1185</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 노적산로 70 2층 모먼트짐 학익점</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jhmomentgym</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>560</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>562</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1122</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1296714905</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1296714905</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>올타임클래식짐 헬스PT 주안도화점</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>all_time_classic@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1372-9682</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 한나루로 604 롯데월드타워오피스텔 B1층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alltimeclassic_gym?igsh=cWV5d3BqdXF2MHI4&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>214</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>97</v>
+      </c>
+      <c r="R39" t="n">
+        <v>311</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>2001570240</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001570240</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>바디에이프PT&amp;헬스 주안점</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>apecompany@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0507-1321-5947</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 석정로 430 3층</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/apecompany</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>401</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>299</v>
+      </c>
+      <c r="R40" t="n">
+        <v>700</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1479770189</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1479770189</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>아이언짐</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>irongyms@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>070-8680-2996</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 100 2층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/irongym_inha/</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>12</v>
+      </c>
+      <c r="R41" t="n">
+        <v>19</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1814450633</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1814450633</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>유니크휘트니스</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ptkoogold@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>032-891-2300</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 낙섬서로 4</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>4</v>
+      </c>
+      <c r="R42" t="n">
+        <v>18</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>19456559</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19456559</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>피트니스 연구소 인하대역점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>lfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1441-2226</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로 309 노블레스타워 8층 피트니스 연구소 인하대역점</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>http://www.fitnessinstitute.co.kr/</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>2764</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>373</v>
+      </c>
+      <c r="R43" t="n">
+        <v>3137</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1562966214</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1562966214</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>511 GYM</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>92shout@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>032-873-0511</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 한나루로 468</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>10</v>
+      </c>
+      <c r="R44" t="n">
+        <v>44</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>293777145</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/293777145</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>핏앤랑 용현점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>rangfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1312-1148</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 용현동 685-12 6층 핏앤랑 용현점</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://hangeulcaesbos-jy01076096309.replit.app</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>609</v>
+      </c>
+      <c r="R45" t="n">
+        <v>697</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1895375636</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1895375636</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>머슬앤피플 헬스&amp;PT 학익점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>b970610@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 매소홀로 388 유니스프라자 4층 머슬앤피플 학익점</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muscle_people_hagik</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>397</v>
+      </c>
+      <c r="R46" t="n">
+        <v>471</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1614382732</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614382732</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>투모로우짐 주안간석점</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>tomorrowgym_2@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1391-7433</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안로 171 101동 101호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tomorrowgym_2</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>569</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>390</v>
+      </c>
+      <c r="R47" t="n">
+        <v>959</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1990295249</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1990295249</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>중앙헬스케어</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>mujini2358@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>032-874-8111</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 한나루로 389</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>9</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1216392196</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1216392196</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>네이비짐 용현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>navygym8296@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1484-8297</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 토금남로 84 제일프라자 7층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/navygym8296</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>267</v>
+      </c>
+      <c r="R49" t="n">
+        <v>387</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1635596526</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1635596526</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CBBM휘트니스센타</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>csys026@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독정이로 40 4층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1707568333</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1707568333</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>휘트니스88 헬스 PT 간석점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>fitness_88@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1497-8905</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 석산로 12 뉴스타빌딩 3층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitness_88</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>584</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>835</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1419</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1833832072</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1833832072</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>펀휘트니스 학익점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>funfitness7400@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1449-7400</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 소성로185번길 16-20 대승빌딩 5층 FUN휘트니스</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>http://funfitness3.alltheway.kr/</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>880</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2103</v>
+      </c>
+      <c r="R52" t="n">
+        <v>2983</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>34658737</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34658737</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>그레이짐&amp;기구필라테스</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>kaafsong@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1443-9012</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 아암대로 101 1층3층</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kaafsong</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>190</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>196</v>
+      </c>
+      <c r="R53" t="n">
+        <v>386</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1581440318</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1581440318</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>투모로우짐 용현점 24시 헬스장</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>baekho_94@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1367-7433</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인주대로 124 3층 전체, 4층 일부</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/baekho_94</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>644</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>365</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1009</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1016324075</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1016324075</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>크로스핏 주안</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>cfjuan1@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>032-429-9997</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안로 100 B1 크로스핏주안</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/cfjuan1</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>464</v>
+      </c>
+      <c r="R55" t="n">
+        <v>537</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>37050088</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37050088</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>크로스핏 피포피 주안점</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>bow14674@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로184번길 4 1층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bow14674</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>70</v>
+      </c>
+      <c r="R56" t="n">
+        <v>246</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>1132783494</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1132783494</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>바디와이짐 용현동PT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>707seal1@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>070-8995-9696</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 107 2층 바디와이짐</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/707seal1</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>192</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>84</v>
+      </c>
+      <c r="R57" t="n">
+        <v>276</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1526339691</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1526339691</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>070-4594-5264</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 문학동</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1687335087</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1687335087</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>서울헬스케어</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ellysdoctor@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>032-230-3889</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안동 1559-29</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>670</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2</v>
+      </c>
+      <c r="R59" t="n">
+        <v>672</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>1984269229</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1984269229</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>우피짐 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>whoopeeasd@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0507-1393-0612</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 620 2층</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/whoopeeasd</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>86</v>
+      </c>
+      <c r="R60" t="n">
+        <v>286</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1914109352</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1914109352</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>플렉스짐</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>flexgym_3@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1373-9688</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 594 동경프라자 4층</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/flexgym_3</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>5</v>
+      </c>
+      <c r="R61" t="n">
+        <v>5</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>2072976485</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2072976485</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>인싸짐 학익점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>inssagym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1333-3818</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 매소홀로 474 4층, 5층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/12/bizes/819286/items/4778701?preview=1</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>1338</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>1960</v>
+      </c>
+      <c r="R62" t="n">
+        <v>3298</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1303371206</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1303371206</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>올피플 24시 헬스 PT 주안 구월점</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>allpeople_juan@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경원대로 768 7층</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_bHxown</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>629</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1072</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>2061644044</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2061644044</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>블랙짐</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>alsgh9226@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1484-9699</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 301 블랙짐 6층</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>21</v>
+      </c>
+      <c r="R64" t="n">
+        <v>53</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>32999004</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32999004</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>홍휘트니스</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0leejieun@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0507-1433-2100</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 염창로 46 강남메디컬타워 8층</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>http://hongfitness.itpage.kr</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>108</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>98</v>
+      </c>
+      <c r="R65" t="n">
+        <v>206</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>38301772</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38301772</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>짐토스</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>gymtos_juan@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0507-1349-8372</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 177 5, 6층</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymtos_juan</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>27</v>
+      </c>
+      <c r="R66" t="n">
+        <v>178</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>2067646367</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2067646367</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>무무짐용현점 헬스장PT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>moomoogym_2@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1599-9949</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 낙섬서로 4 7층 701호, 702호</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/moomoogym_2</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>421</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1521</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>1934281926</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1934281926</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>와이짐 주안역점</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>successful09@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>032-208-9600</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안로 113 덕진빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/successful09</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>142</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>264</v>
+      </c>
+      <c r="R68" t="n">
+        <v>406</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>13534760</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13534760</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>구민체육센터</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>미추홀구국민체육센터</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>tong_namgu@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>032-225-2070</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로42번길 57</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://sports.imfm.or.kr</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>637</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>121</v>
+      </c>
+      <c r="R69" t="n">
+        <v>758</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1782028998</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1782028998</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>목욕탕,사우나</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>신성불가마사우나 &amp; 만화</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>jnl0307@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>032-420-0211</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안중로 25 지하1층</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>18</v>
+      </c>
+      <c r="R70" t="n">
+        <v>256</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>11821419</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11821419</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>수영장</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>에이스스포츠센터</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>jmsd1104@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>032-422-4420</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 434 제일빌딩</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jmsd1104</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>456</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>55</v>
+      </c>
+      <c r="R71" t="n">
+        <v>511</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>31793861</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31793861</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>어게인핏 PT 주안점</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>yeoninmo@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0507-1394-8036</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 구월로40번길 4 2층 어게인핏</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/again_fit_juan?igsh=cGJremczeG83cTA%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>125</v>
+      </c>
+      <c r="R72" t="n">
+        <v>197</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1470836324</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1470836324</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>베럴핏 용현점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>betterfitpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1401-5990</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 매소홀로 63 대신프라자 702호 베럴핏</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/betterfitpt</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>173</v>
+      </c>
+      <c r="R73" t="n">
+        <v>253</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>37890204</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37890204</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>와이키키 트레이닝클럽</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>waikiki_trainingclub@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0507-1489-8101</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 87-1 B1</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/waikiki_trainingclub_inha</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>82</v>
+      </c>
+      <c r="R74" t="n">
+        <v>123</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1324912852</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1324912852</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>바름핏 pt&amp;필라테스 주안점</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>brfpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0507-1490-4455</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인주대로 370 7층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bareumfit/</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>124</v>
+      </c>
+      <c r="R75" t="n">
+        <v>179</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>1623977840</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1623977840</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>PT의품격 용현점</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>jaeyounggom@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0507-1445-6077</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 아암대로45번길 77-8 2층 201호</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jaeyounggom</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>336</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>399</v>
+      </c>
+      <c r="R76" t="n">
+        <v>735</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>1048465766</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1048465766</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>바름핏 PT&amp;필라테스 본점</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>brfpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1455-8691</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 소성로 150 2층바름핏</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/brfpt</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>358</v>
+      </c>
+      <c r="R77" t="n">
+        <v>638</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1493566392</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1493566392</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>레몬짐 용현점</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>lafcompany_@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1373-2249</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로 311 비젼프라자 11층 레몬짐 용현점</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>http://www.lemongym.co.kr</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>362</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>11</v>
+      </c>
+      <c r="R78" t="n">
+        <v>373</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1984607952</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1984607952</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>뉴케이와이피트니스</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>5830666@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0505-720-1633</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 510 지하1층</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>2090228880</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2090228880</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>저스트PT짐</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>rlaehgus1236@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1379-2006</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로317번길 29 11층</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlaehgus1236</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>209</v>
+      </c>
+      <c r="R80" t="n">
+        <v>328</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1324594280</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1324594280</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>뉴바디짐</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>godanhe@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>032-710-1633</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로317번길 23 해성프라자 6층 뉴바디짐</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_yyvMxb/chat</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>31</v>
+      </c>
+      <c r="R81" t="n">
+        <v>109</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1357445067</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1357445067</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>더케어핏</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>thecarefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1346-7187</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 346 2층 더케어핏</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/thecarefit</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>16</v>
+      </c>
+      <c r="R82" t="n">
+        <v>74</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1879252749</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1879252749</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>쎈 PT 스튜디오 인천도화점</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ssenptstudio@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1362-0833</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로87번길 2 센타프라자 203호</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ssenptstudio</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>50</v>
+      </c>
+      <c r="R83" t="n">
+        <v>275</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1691655395</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1691655395</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>도모 스트렝스</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>5tokoda@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1334-7275</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 석정로 244 지하1층</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@Domo_otokoda?si=vWR7lJmjGYe0J-VO</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>273</v>
+      </c>
+      <c r="R84" t="n">
+        <v>320</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1628768408</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628768408</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>국가대표 박인정 PT샵 주안본점</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>powerman962@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로325번길 27 미추홀더리브아파트 상가 2F</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pij_pt_shop</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>41</v>
+      </c>
+      <c r="R85" t="n">
+        <v>136</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1611506975</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1611506975</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>코코PT스튜디오</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>skywjdska@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1415-5400</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안로205번길 12-22 3층 코코PT피티</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/skywjdska</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>75</v>
+      </c>
+      <c r="R86" t="n">
+        <v>106</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1585011100</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1585011100</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>라프그라운드 인하대역 본점</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>lafground@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1418-2258</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로 309 노블레스타워 7층 703호</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>http://lafground.com</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>187</v>
+      </c>
+      <c r="R87" t="n">
+        <v>330</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>1011248917</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1011248917</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>클럽사이클 인하대역 본점</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>clubcycle_inha@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1396-1335</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로 311 1102호</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://clubcycle.co.kr/</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>288</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>122</v>
+      </c>
+      <c r="R88" t="n">
+        <v>410</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1405261682</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1405261682</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>진스 핏</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>jeansfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1399-8039</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 84 4층</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jeans_fit77?igsh=cXg0ZTZ0N203emlt</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>2</v>
+      </c>
+      <c r="R89" t="n">
+        <v>42</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>2036358510</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2036358510</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>프레임짐</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>framegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>032-423-6682</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 372 201동 2층 2105호,2106호(주안동, 포레나 미추홀)</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/framegym</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>61</v>
+      </c>
+      <c r="R90" t="n">
+        <v>107</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>1519782630</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1519782630</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>모두짐 재활PT 인천도화점</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>modoo2206@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0507-1484-5789</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로87번길 28-1 다온1프라자 5층 모두짐 인천도화점</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@mutongweight</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>323</v>
+      </c>
+      <c r="R91" t="n">
+        <v>561</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1514606541</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1514606541</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>유코치의슬림해짐</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>syhs007@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1465-4459</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 제일로 31 상가 2층 205호</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yoocoach007</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>30</v>
+      </c>
+      <c r="R92" t="n">
+        <v>46</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>1250104868</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1250104868</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>카트로폴리스 스포츠</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>redleopard963@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1367-2605</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 100 대운동장</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>http://castorpullussports.hiadmaker.kr</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>41</v>
+      </c>
+      <c r="R93" t="n">
+        <v>41</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1353161485</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1353161485</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>본어게인</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>born_again2020@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1346-9775</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 소성로185번길 12 평산빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/born_again2020</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>232</v>
+      </c>
+      <c r="R94" t="n">
+        <v>336</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1825358057</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1825358057</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>루트짐 주안점</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>rlawnsgh3347@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1492-1172</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 석정로375번길 11 2층 루트짐 주안점</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlawnsgh3347</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>72</v>
+      </c>
+      <c r="R95" t="n">
+        <v>132</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1765729791</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1765729791</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>크런치핏</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>crunchfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0507-1369-2362</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경원대로 863 서해빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/crunchfit</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>5</v>
+      </c>
+      <c r="R96" t="n">
+        <v>13</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1258852561</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1258852561</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>와이짐휘트니스 신기촌점</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>successful09@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1370-9607</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 304-1 지하1층</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/successful09</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>165</v>
+      </c>
+      <c r="R97" t="n">
+        <v>195</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1390976602</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1390976602</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>유리,창호공사</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>스피드부스</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>juliday@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 아암대로 101</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>http://www.speedbooth.co.kr</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>1</v>
+      </c>
+      <c r="R98" t="n">
+        <v>4</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>21799895</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21799895</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>중개업</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>뉴인천부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>kittymuscle@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>kittymuscle@gmail.com</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경원대로 812-1 뉴인천부동산건물2층</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/sports8948</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>1</v>
+      </c>
+      <c r="R99" t="n">
+        <v>1</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>1761152160</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1761152160</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>흐름필라테스&amp;요가</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>hrmpilayoga@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1470-8448</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 송림로 251 창조프라자 4층</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hrmpilayoga</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
         <v>221</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q100" t="n">
         <v>88</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R100" t="n">
         <v>309</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
         <is>
           <t>1316056634</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U100" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1316056634</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="V100" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/미추홀구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/미추홀구_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="Q2" t="n">
         <v>724</v>
       </c>
       <c r="R2" t="n">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
         <v>443</v>
       </c>
       <c r="Q6" t="n">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="R6" t="n">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2777</v>
+        <v>2779</v>
       </c>
       <c r="Q7" t="n">
         <v>377</v>
       </c>
       <c r="R7" t="n">
-        <v>3154</v>
+        <v>3156</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1213,39 +1213,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>터닝포인트짐 헬스 PT 주안점</t>
+          <t>워라블짐 헬스 PT 도화점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tpg21@naver.com</t>
+          <t>wlb1203@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1360-9997</t>
+          <t>0507-1405-1273</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 730 고려빌딩 4층</t>
+          <t>인천광역시 미추홀구 경인로 251 3층 워라블짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.tpgymjooan.com/</t>
+          <t>https://blog.naver.com/wlb1203</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1266,7 +1266,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1149</v>
+        <v>150</v>
       </c>
       <c r="Q9" t="n">
-        <v>1391</v>
+        <v>235</v>
       </c>
       <c r="R9" t="n">
-        <v>2540</v>
+        <v>385</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1015443504</t>
+          <t>1596200279</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1015443504</t>
+          <t>https://m.place.naver.com/place/1596200279</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1307,39 +1307,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>워라블짐 헬스 PT 도화점</t>
+          <t>클럽사이클 인하대역 본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>wlb1203@naver.com</t>
+          <t>clubcycle_inha@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1405-1273</t>
+          <t>0507-1396-1335</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 251 3층 워라블짐</t>
+          <t>인천광역시 미추홀구 독배로 311 1102호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wlb1203</t>
+          <t>https://clubcycle.co.kr/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1360,7 +1360,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>150</v>
+        <v>293</v>
       </c>
       <c r="Q10" t="n">
-        <v>235</v>
+        <v>126</v>
       </c>
       <c r="R10" t="n">
-        <v>385</v>
+        <v>419</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,15 +1384,113 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1596200279</t>
+          <t>1405261682</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596200279</t>
+          <t>https://m.place.naver.com/place/1405261682</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>필라테스 린 용현점</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>pilatelean_yonghyeon@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1436-2046</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>인천 미추홀구 독배로317번길 29 컬러프라자 10층</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://instabio.cc/pilateslean</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4d93x</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>496</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>417</v>
+      </c>
+      <c r="R11" t="n">
+        <v>913</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1650855814</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1650855814</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/미추홀구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/미추홀구_헬스장.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="Q2" t="n">
         <v>724</v>
       </c>
       <c r="R2" t="n">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="Q4" t="n">
         <v>1230</v>
       </c>
       <c r="R4" t="n">
-        <v>2819</v>
+        <v>2821</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1030,29 +1030,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피트니스 연구소 인하대역점</t>
+          <t>인싸짐 학익점 헬스 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lfitness@naver.com</t>
+          <t>inssagym2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1441-2226</t>
+          <t>0507-1333-3818</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 309 노블레스타워 8층 피트니스 연구소 인하대역점</t>
+          <t>인천광역시 미추홀구 매소홀로 474 4층, 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.fitnessinstitute.co.kr/</t>
+          <t>https://booking.naver.com/booking/12/bizes/819286/items/4778701?preview=1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2779</v>
+        <v>1349</v>
       </c>
       <c r="Q7" t="n">
-        <v>377</v>
+        <v>1979</v>
       </c>
       <c r="R7" t="n">
-        <v>3156</v>
+        <v>3328</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1562966214</t>
+          <t>1303371206</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1562966214</t>
+          <t>https://m.place.naver.com/place/1303371206</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1124,29 +1124,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>포텐휘트니스</t>
+          <t>라이노짐 인천도화점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jyj09623@naver.com</t>
+          <t>smhon833@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1336-2892</t>
+          <t>0507-1349-3268</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 토금중로 13 4층</t>
+          <t>인천광역시 미추홀구 송림로 249 새마을금고 3층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://linktr.ee/fitness410</t>
+          <t>https://blog.naver.com/smhon833</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="R8" t="n">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1932083996</t>
+          <t>1098224618</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1932083996</t>
+          <t>https://m.place.naver.com/place/1098224618</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1218,29 +1218,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>워라블짐 헬스 PT 도화점</t>
+          <t>플렉스짐</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>wlb1203@naver.com</t>
+          <t>flexgym_3@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1405-1273</t>
+          <t>0507-1373-9688</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 251 3층 워라블짐</t>
+          <t>인천광역시 미추홀구 미추홀대로 594 동경프라자 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wlb1203</t>
+          <t>https://www.instagram.com/flexgym_3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>235</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>385</v>
+        <v>6</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1596200279</t>
+          <t>2072976485</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596200279</t>
+          <t>https://m.place.naver.com/place/2072976485</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1307,34 +1307,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>클럽사이클 인하대역 본점</t>
+          <t>무무짐 헬스PT 학익점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>clubcycle_inha@naver.com</t>
+          <t>moomoogym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1396-1335</t>
+          <t>0507-1308-5406</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 311 1102호</t>
+          <t>인천광역시 미추홀구 매소홀로 446 대성빌딩 6층 601호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://clubcycle.co.kr/</t>
+          <t>http://pf.kakao.com/_DaIdn</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>293</v>
+        <v>956</v>
       </c>
       <c r="Q10" t="n">
-        <v>126</v>
+        <v>517</v>
       </c>
       <c r="R10" t="n">
-        <v>419</v>
+        <v>1473</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1405261682</t>
+          <t>1676785771</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1405261682</t>
+          <t>https://m.place.naver.com/place/1676785771</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/미추홀구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/미추홀구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,49 +559,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>인터넷상거래</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피트니스 연구소 용현점 헬스 PT</t>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lfitness3@naver.com</t>
+          <t>bizhows@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1327-2357</t>
+          <t>070-8904-7687</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 인주대로 68 예승프라자 4층, 5층</t>
+          <t>인천광역시 미추홀구 문학동</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.fitnessinstitute.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -612,22 +612,22 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1726</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>724</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2450</v>
+        <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1279263313</t>
+          <t>1125776238</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1279263313</t>
+          <t>https://m.place.naver.com/place/1125776238</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>웨이빗 피트니스 24시 헬스 PT 주안점</t>
+          <t>케이짐 인천도화점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>weibit@naver.com</t>
+          <t>la4200@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1328-8048</t>
+          <t>0507-1459-0283</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 716 6층 웨이빗 피트니스</t>
+          <t>인천광역시 미추홀구 염전로202번길 59 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/weibit_official</t>
+          <t>https://blog.naver.com/la4200</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2917</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
-        <v>782</v>
+        <v>43</v>
       </c>
       <c r="R3" t="n">
-        <v>3699</v>
+        <v>66</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1700131075</t>
+          <t>1115746281</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700131075</t>
+          <t>https://m.place.naver.com/place/1115746281</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -752,34 +752,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>인싸짐 주안점</t>
+          <t>크로스핏 히든라인</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>inssagym3@naver.com</t>
+          <t>crossfit_hiddenline@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1332-3818</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로 848 지하2층</t>
+          <t>인천광역시 미추홀구 미추홀대로 696 지하1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/5/bizes/840698?area=pll&amp;service-target=map-pc&amp;theme=place</t>
+          <t>https://blog.naver.com/crossfit_hiddenline</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +785,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1591</v>
+        <v>85</v>
       </c>
       <c r="Q4" t="n">
-        <v>1230</v>
+        <v>38</v>
       </c>
       <c r="R4" t="n">
-        <v>2821</v>
+        <v>123</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1070990223</t>
+          <t>1178767303</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070990223</t>
+          <t>https://m.place.naver.com/place/1178767303</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,34 +842,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>플렉스짐</t>
+          <t>올피플 24시 헬스 PT 주안 구월점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flexgym_1@naver.com</t>
+          <t>allpeople_juan@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0507-1441-2280</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 392 경인상가 3층</t>
+          <t>인천광역시 미추홀구 경원대로 768 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/flexgym_1</t>
+          <t>http://pf.kakao.com/_bHxown</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +875,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +895,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>670</v>
+        <v>444</v>
       </c>
       <c r="Q5" t="n">
-        <v>237</v>
+        <v>650</v>
       </c>
       <c r="R5" t="n">
-        <v>907</v>
+        <v>1094</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13309652</t>
+          <t>2061644044</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13309652</t>
+          <t>https://m.place.naver.com/place/2061644044</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -940,35 +932,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>올피플 24시 헬스 PT 주안 구월점</t>
+          <t>서울헬스케어</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>allpeople_juan@naver.com</t>
+          <t>ellysdoctor@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>032-230-3889</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로 768 7층</t>
+          <t>인천광역시 미추홀구 주안동 1559-29</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_bHxown</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -984,22 +980,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>443</v>
+        <v>670</v>
       </c>
       <c r="Q6" t="n">
-        <v>649</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>1092</v>
+        <v>672</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2061644044</t>
+          <t>1984269229</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061644044</t>
+          <t>https://m.place.naver.com/place/1984269229</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1030,34 +1026,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인싸짐 학익점 헬스 PT</t>
+          <t>팀크루즈 역도체육관&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>inssagym2@naver.com</t>
+          <t>team_cruise@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1333-3818</t>
+          <t>0507-1341-0981</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 474 4층, 5층</t>
+          <t>인천광역시 미추홀구 인주대로 438 삼영빌딩 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/819286/items/4778701?preview=1</t>
+          <t>https://www.instagram.com/teamcruise_juan/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1067,7 +1063,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1078,7 +1074,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1349</v>
+        <v>64</v>
       </c>
       <c r="Q7" t="n">
-        <v>1979</v>
+        <v>21</v>
       </c>
       <c r="R7" t="n">
-        <v>3328</v>
+        <v>85</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1303371206</t>
+          <t>1455972728</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303371206</t>
+          <t>https://m.place.naver.com/place/1455972728</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>라이노짐 인천도화점</t>
+          <t>바디와이짐 용현동PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>smhon833@naver.com</t>
+          <t>707seal1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1349-3268</t>
+          <t>070-8995-9696</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 송림로 249 새마을금고 3층</t>
+          <t>인천광역시 미추홀구 인하로 107 2층 바디와이짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/smhon833</t>
+          <t>https://blog.naver.com/707seal1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,17 +1173,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="Q8" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="R8" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1098224618</t>
+          <t>1526339691</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098224618</t>
+          <t>https://m.place.naver.com/place/1526339691</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1214,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>플렉스짐</t>
+          <t>와이짐 주안역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>flexgym_3@naver.com</t>
+          <t>successful09@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1373-9688</t>
+          <t>032-208-9600</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 594 동경프라자 4층</t>
+          <t>인천광역시 미추홀구 주안로 113 덕진빌딩 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/flexgym_3</t>
+          <t>https://blog.naver.com/successful09</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1251,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>264</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>407</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2072976485</t>
+          <t>13534760</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072976485</t>
+          <t>https://m.place.naver.com/place/13534760</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1312,34 +1308,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>무무짐 헬스PT 학익점</t>
+          <t>휘트니스88 헬스 PT 간석점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>moomoogym@naver.com</t>
+          <t>fitness_88@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1308-5406</t>
+          <t>0507-1497-8905</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 446 대성빌딩 6층 601호</t>
+          <t>인천광역시 미추홀구 석산로 12 뉴스타빌딩 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_DaIdn</t>
+          <t>https://blog.naver.com/fitness_88</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1349,7 +1345,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1360,7 +1356,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1369,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>956</v>
+        <v>584</v>
       </c>
       <c r="Q10" t="n">
-        <v>517</v>
+        <v>837</v>
       </c>
       <c r="R10" t="n">
-        <v>1473</v>
+        <v>1421</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,56 +1380,56 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1676785771</t>
+          <t>1833832072</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1676785771</t>
+          <t>https://m.place.naver.com/place/1833832072</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>필라테스 린 용현점</t>
+          <t>워라블짐 헬스 PT 도화점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pilatelean_yonghyeon@naver.com</t>
+          <t>wlb1203@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1436-2046</t>
+          <t>0507-1405-1273</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천 미추홀구 독배로317번길 29 컬러프라자 10층</t>
+          <t>인천광역시 미추홀구 경인로 251 3층 워라블짐</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://instabio.cc/pilateslean</t>
+          <t>https://blog.naver.com/wlb1203</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1443,19 +1439,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4d93x</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1459,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>496</v>
+        <v>150</v>
       </c>
       <c r="Q11" t="n">
-        <v>417</v>
+        <v>235</v>
       </c>
       <c r="R11" t="n">
-        <v>913</v>
+        <v>385</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1474,8959 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1650855814</t>
+          <t>1596200279</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1650855814</t>
+          <t>https://m.place.naver.com/place/1596200279</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>바디에이프PT&amp;헬스 주안점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>apecompany@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1321-5947</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 석정로 430 3층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/apecompany</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>408</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>302</v>
+      </c>
+      <c r="R12" t="n">
+        <v>710</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1479770189</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1479770189</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>올스타짐 헬스 PT 도화점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>allstargym_dohwa@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1426-4489</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로 93 로데오플라자 4층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_juCxmxj/chat</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>443</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>246</v>
+      </c>
+      <c r="R13" t="n">
+        <v>689</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1468509783</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1468509783</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>올타임클래식짐 헬스PT 주안도화점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>all_time_classic@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1372-9682</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 한나루로 604 롯데월드타워오피스텔 B1층</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/alltimeclassic_gym?igsh=cWV5d3BqdXF2MHI4&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>101</v>
+      </c>
+      <c r="R14" t="n">
+        <v>322</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2001570240</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2001570240</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CBBM휘트니스센타</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>csys026@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독정이로 40 4층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1707568333</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1707568333</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>하이엔드 휘트니스 주안</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>highendfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1477-3415</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경원대로 869 르네상스타워 19층 하이엔드 휘트니스</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>http://www.highendfitness.kr/</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>522</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>184</v>
+      </c>
+      <c r="R16" t="n">
+        <v>706</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1851949492</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1851949492</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>그레이짐&amp;기구필라테스</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>kaafsong@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1443-9012</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 아암대로 101 1층3층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kaafsong</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>193</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>201</v>
+      </c>
+      <c r="R17" t="n">
+        <v>394</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1581440318</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1581440318</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>클럽훈짐 제물포점</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>clubhungym@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>032-891-1124</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 119 4층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/clubhungym</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>477</v>
+      </c>
+      <c r="R18" t="n">
+        <v>554</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>37696077</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37696077</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>유니크휘트니스</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ptkoogold@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>032-891-2300</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 낙섬서로 4</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4</v>
+      </c>
+      <c r="R19" t="n">
+        <v>18</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>19456559</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19456559</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>아이언짐</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>irongyms@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>070-8680-2996</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 100 2층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/irongym_inha/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>12</v>
+      </c>
+      <c r="R20" t="n">
+        <v>19</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1814450633</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1814450633</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>바른습관PT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>hyptjuan@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1466-0535</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 염창로 65 4층 바른습관 PT STUDIO</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mgm_hypt?igsh=ODA1NTc5OTg5Nw%3D%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>69</v>
+      </c>
+      <c r="R21" t="n">
+        <v>175</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1761795724</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1761795724</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>포멀짐 헬스&amp;피티 제물포점</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>formalgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1365-5941</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 128 2층 포멀짐</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/formalgym</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>9</v>
+      </c>
+      <c r="R22" t="n">
+        <v>111</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1933593128</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1933593128</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>투모로우짐 주안간석점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>tomorrowgym_2@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1391-7433</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안로 171 101동 101호</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/tomorrowgym_2</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>568</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>393</v>
+      </c>
+      <c r="R23" t="n">
+        <v>961</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1990295249</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1990295249</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>왕삼두짐 용현점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>kingtricepsgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1427-2029</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 낙섬중로 67 3층 왕삼두짐</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kingtricepsgym</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>413</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1026</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1439</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>85538155</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/85538155</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>짐토스24시 주안점</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>gymtos_juan@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1349-8372</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 177 5, 6층</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gymtos_juan</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>41</v>
+      </c>
+      <c r="R25" t="n">
+        <v>217</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2067646367</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2067646367</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>피트니스 연구소 인하대역점</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>lfitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1441-2226</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로 309 노블레스타워 8층 피트니스 연구소 인하대역점</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>http://www.fitnessinstitute.co.kr/</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>2782</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>377</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3159</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1562966214</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1562966214</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>모먼트짐 학익점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>jhmomentgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1340-1185</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 노적산로 70 2층 모먼트짐 학익점</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jhmomentgym</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>575</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1150</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1296714905</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1296714905</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>크로스핏 피포피 주안점</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>bow14674@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로184번길 4 1층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bow14674</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>70</v>
+      </c>
+      <c r="R28" t="n">
+        <v>246</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1132783494</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1132783494</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>더짐휘트니스 PT&amp;기구필라테스&amp;스피닝</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>thegymtf@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>032-439-3456</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경원대로 740 광성스포렉스 2, 3층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thegym__fit</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>149</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>49</v>
+      </c>
+      <c r="R29" t="n">
+        <v>198</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>36339144</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36339144</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>제이짐휘트니스 주안점</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>csys026@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1330-7817</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 길파로 7 주안프라자 7층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_gxbxkhG/chat</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>25</v>
+      </c>
+      <c r="R30" t="n">
+        <v>125</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1927377740</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1927377740</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>중앙헬스케어</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mujini2358@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>032-874-8111</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 한나루로 389</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>9</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1216392196</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1216392196</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>블랙짐</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>alsgh9226@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1484-9699</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 301 블랙짐 6층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>21</v>
+      </c>
+      <c r="R32" t="n">
+        <v>53</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>32999004</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32999004</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>터닝포인트짐 헬스 PT 주안점</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>tpg21@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0507-1360-9997</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 730 고려빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.tpgymjooan.com/</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>1149</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1391</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2540</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1015443504</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1015443504</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>플렉스짐</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>flexgym_3@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1373-9688</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 594 동경프라자 4층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/flexgym_3</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>2072976485</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2072976485</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>와이키키짐 PT 주안점</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>waikikigym2311@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1365-4408</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 710 지하1층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/waikikigym_jwsong?igsh=bG51c2U5anlmZ2Ez&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>121</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1533</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1654</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1085067011</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1085067011</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>인싸짐 학익점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>inssagym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1333-3818</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 매소홀로 474 4층, 5층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://booking.naver.com/booking/12/bizes/819286/items/4778701?preview=1</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>1349</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1980</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3329</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>1303371206</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1303371206</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>070-8904-0130</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안동</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1572489627</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1572489627</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>에이짐 용현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>agym_11@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1340-2343</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 아암대로29번길 47 4,5층 AGYM용현점</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/a_gym11/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>267</v>
+      </c>
+      <c r="R38" t="n">
+        <v>458</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1560921815</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1560921815</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>크로스핏 온드트레이닝클럽</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ondtrainingclub@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0507-1368-6596</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 구월로37번길 30 1층 온드트레이닝클럽</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ondtrainingclub</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>57</v>
+      </c>
+      <c r="R39" t="n">
+        <v>128</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>1606082108</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1606082108</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>070-8904-9495</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 도화동</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1642236752</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1642236752</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>우피짐 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>whoopeeasd@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1393-0612</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 620 2층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/whoopeeasd</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>93</v>
+      </c>
+      <c r="R41" t="n">
+        <v>295</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1914109352</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1914109352</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>동익인간 원스텝짐_도화동 헬스장&amp;PT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>godblessjiyu@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1420-5777</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로95번길 19 영프라자3차 3층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/godblessjiyu</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>351</v>
+      </c>
+      <c r="R42" t="n">
+        <v>453</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1374352371</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1374352371</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>인터넷상거래</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>070-8904-0824</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 관교동</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1388028605</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1388028605</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>현헬스</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kingkong-play@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>032-863-8673</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 제일로 48 3층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kingkong-play</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>23</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1145507902</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1145507902</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>넘버제로짐 헬스&amp;PT 주안역점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sid1287@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1363-2606</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 725 5층</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/no.0pt/</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>515</v>
+      </c>
+      <c r="R45" t="n">
+        <v>846</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1326633826</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1326633826</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>타임짐 헬스 PT 간석점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>timegym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0507-1473-5883</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 석산로 36 한빛프라자 지하B1 타임짐 주안간석점</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/timegym2</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>654</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>281</v>
+      </c>
+      <c r="R46" t="n">
+        <v>935</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1746753643</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1746753643</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>투모로우짐 용현점 24시 헬스장</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>baekho_94@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1367-7433</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인주대로 124 3층 전체, 4층 일부</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/baekho_94</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>644</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>367</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1011</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1016324075</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1016324075</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>에이지트레이닝피티 주안점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ag_training@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1305-5338</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로325번길 27 3층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ag_training</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>2007007809</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2007007809</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>플렉스짐</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>flexgym_1@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1441-2280</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 392 경인상가 3층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/flexgym_1</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>670</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>237</v>
+      </c>
+      <c r="R49" t="n">
+        <v>907</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>13309652</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/13309652</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>511 GYM</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>92shout@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>032-873-0511</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 한나루로 468</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>10</v>
+      </c>
+      <c r="R50" t="n">
+        <v>44</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>293777145</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/293777145</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>인싸짐 주안점</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>inssagym3@naver.com</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0507-1332-3818</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경원대로 848 지하2층</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://m.booking.naver.com/booking/5/bizes/840698?area=pll&amp;service-target=map-pc&amp;theme=place</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>1591</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1231</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2822</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>1070990223</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1070990223</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>라이노짐 인천도화점</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>smhon833@naver.com</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0507-1349-3268</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 송림로 249 새마을금고 3층</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/smhon833</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>86</v>
+      </c>
+      <c r="R52" t="n">
+        <v>262</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>1098224618</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1098224618</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>척척본피트니스 &amp; 필라테스</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>chukchukbonefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1491-8872</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로88번길 12 엘리웨이 7BL 3층 38~44호</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/chukchukbonefit</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>297</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>81</v>
+      </c>
+      <c r="R53" t="n">
+        <v>378</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>1337118578</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1337118578</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>웨이빗 피트니스 24시 헬스 PT 주안점</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>weibit@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0507-1328-8048</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 716 6층 웨이빗 피트니스</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/weibit_official</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>2917</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>782</v>
+      </c>
+      <c r="R54" t="n">
+        <v>3699</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1700131075</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1700131075</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>무무짐 헬스PT 학익점</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>moomoogym@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>0507-1308-5406</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 매소홀로 446 대성빌딩 6층 601호</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_DaIdn</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P55" t="n">
+        <v>956</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>518</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1474</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>1676785771</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1676785771</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>홍휘트니스</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0leejieun@naver.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0507-1433-2100</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 염창로 46 강남메디컬타워 8층</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>http://hongfitness.itpage.kr</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>101</v>
+      </c>
+      <c r="R56" t="n">
+        <v>212</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>38301772</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/38301772</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>포텐휘트니스</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>jyj09623@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1336-2892</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 토금중로 13 4층</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/fitness410</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>161</v>
+      </c>
+      <c r="R57" t="n">
+        <v>287</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>1932083996</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1932083996</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>바디와이짐&amp;라필라테스 용현동헬스</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>707seal1@naver.com</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>0507-1334-8283</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 용정공원로83번길 59 드림빌딩 8층</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/707seal1</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P58" t="n">
+        <v>1095</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>221</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1316</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>1293988349</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1293988349</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>크로스핏 주안</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>cfjuan1@naver.com</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>032-429-9997</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안로 100 B1 크로스핏주안</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/cfjuan1</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P59" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>469</v>
+      </c>
+      <c r="R59" t="n">
+        <v>542</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>37050088</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37050088</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>머슬앤피플 헬스&amp;PT 학익점</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>b970610@naver.com</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 매소홀로 388 유니스프라자 4층 머슬앤피플 학익점</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/muscle_people_hagik</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P60" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>403</v>
+      </c>
+      <c r="R60" t="n">
+        <v>477</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>1614382732</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1614382732</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>피트니스 연구소 용현점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>lfitness3@naver.com</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1327-2357</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인주대로 68 예승프라자 4층, 5층</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.fitnessinstitute.co.kr/</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P61" t="n">
+        <v>1727</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>724</v>
+      </c>
+      <c r="R61" t="n">
+        <v>2451</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>1279263313</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1279263313</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>네이비짐 용현점 헬스PT</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>navygym8296@naver.com</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1484-8297</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 토금남로 84 제일프라자 7층</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/navygym8296</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P62" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>269</v>
+      </c>
+      <c r="R62" t="n">
+        <v>389</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>1635596526</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1635596526</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>카달로그인쇄</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>070-4542-5854</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 관교동</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>1477621152</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1477621152</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>핏앤랑 용현점</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>rangfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1312-1148</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 용현동 685-12 6층 핏앤랑 용현점</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://hangeulcaesbos-jy01076096309.replit.app</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>577</v>
+      </c>
+      <c r="R64" t="n">
+        <v>666</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>1895375636</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1895375636</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>070-4572-4943</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안동</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>1975777980</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1975777980</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>070-4572-4960</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 도화동</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>1540469631</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1540469631</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>삼성헬스클럽</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2601120@naver.com</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>032-868-3355</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 255 3층</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P67" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3</v>
+      </c>
+      <c r="R67" t="n">
+        <v>16</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>36654816</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/36654816</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>광고대행</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>전단지배포대행업체헬스장학원전문가족전단</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>bizhows@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>070-4594-5480</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 문학동</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>1134650118</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1134650118</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>머신 휘트니스</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>skskalwkdwkd@naver.com</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>0507-1387-8943</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인남길30번길 65 4층 머신휘트니스</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/skskalwkdwkd/223808653919</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>17</v>
+      </c>
+      <c r="R69" t="n">
+        <v>49</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>1275261908</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1275261908</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>펀휘트니스 학익점 헬스 PT</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>funfitness7400@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0507-1449-7400</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 소성로185번길 16-20 대승빌딩 5층 FUN휘트니스</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>http://funfitness3.alltheway.kr/</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc3mkt</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>884</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2126</v>
+      </c>
+      <c r="R70" t="n">
+        <v>3010</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>34658737</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/34658737</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>케렌시아피트니스 &amp; 필라테스 주안간석점</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>querencia_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1481-1217</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안로 219 브라이튼 빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wex3fgx</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>131</v>
+      </c>
+      <c r="R71" t="n">
+        <v>167</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>1020929907</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1020929907</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>무무짐용현점 헬스장PT</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>moomoogym_2@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1599-9949</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 낙섬서로 4 7층 701호, 702호</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4e25c</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>1120</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>431</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1551</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>1934281926</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1934281926</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>온핏</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sky41006@naver.com</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0507-1326-0513</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 매소홀로 419 401호</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>2079869378</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2079869378</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>구민체육센터</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>미추홀구국민체육센터</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>rjadmswktjr@naver.com</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>032-225-2070</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로42번길 57</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://sports.imfm.or.kr</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P74" t="n">
+        <v>637</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>122</v>
+      </c>
+      <c r="R74" t="n">
+        <v>759</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>1782028998</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1782028998</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>목욕탕,사우나</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>신성불가마사우나 &amp; 만화</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>jnl0307@naver.com</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>032-420-0211</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안중로 25 지하1층</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P75" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>18</v>
+      </c>
+      <c r="R75" t="n">
+        <v>258</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>11821419</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11821419</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>수영장</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>에이스스포츠센터</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>jmsd1104@naver.com</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>032-422-4420</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 434 제일빌딩</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jmsd1104</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>459</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>55</v>
+      </c>
+      <c r="R76" t="n">
+        <v>514</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>31793861</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31793861</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>코코PT스튜디오</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>skywjdska@naver.com</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0507-1415-5400</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 주안로205번길 12-22 3층 코코PT피티</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/skywjdska</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P77" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>75</v>
+      </c>
+      <c r="R77" t="n">
+        <v>106</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>1585011100</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1585011100</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PT의품격 용현점</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>jaeyounggom@naver.com</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1445-6077</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 아암대로45번길 77-8 2층 201호</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/jaeyounggom</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P78" t="n">
+        <v>342</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>404</v>
+      </c>
+      <c r="R78" t="n">
+        <v>746</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>1048465766</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1048465766</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>카트로폴리스 스포츠</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>shriek82461@naver.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0507-1367-2605</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 100 대운동장</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>http://castorpullussports.hiadmaker.kr</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>41</v>
+      </c>
+      <c r="R79" t="n">
+        <v>41</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>1353161485</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1353161485</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>국가대표 박인정 PT샵 주안본점</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>powerman962@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로325번길 27 미추홀더리브아파트 상가 2F</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pij_pt_shop</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P80" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>41</v>
+      </c>
+      <c r="R80" t="n">
+        <v>136</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>1611506975</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1611506975</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>본어게인</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>born_again2020@naver.com</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0507-1346-9775</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 소성로185번길 12 평산빌딩 6층</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/born_again2020</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>105</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>232</v>
+      </c>
+      <c r="R81" t="n">
+        <v>337</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>1825358057</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1825358057</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>와이키키 트레이닝클럽</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>waikiki_trainingclub@naver.com</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1489-8101</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 87-1 B1</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/waikiki_trainingclub_inha</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>83</v>
+      </c>
+      <c r="R82" t="n">
+        <v>125</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>1324912852</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1324912852</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>도모 스트렝스</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>5tokoda@naver.com</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1334-7275</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 석정로 244 지하1층</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@Domo_otokoda?si=vWR7lJmjGYe0J-VO</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>273</v>
+      </c>
+      <c r="R83" t="n">
+        <v>320</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>1628768408</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1628768408</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>쎈 PT 스튜디오 인천도화점</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ssenptstudio@naver.com</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0507-1362-0833</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로87번길 2 센타프라자 203호</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ssenptstudio</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>229</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>52</v>
+      </c>
+      <c r="R84" t="n">
+        <v>281</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>1691655395</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1691655395</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>더케어핏</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>thecarefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>0507-1346-7187</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 346 2층 더케어핏</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/thecarefit</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P85" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>16</v>
+      </c>
+      <c r="R85" t="n">
+        <v>74</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>1879252749</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1879252749</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>라프그라운드 인하대역 본점</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>lafground@naver.com</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0507-1418-2258</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로 309 노블레스타워 7층 703호</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>http://lafground.com</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P86" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>187</v>
+      </c>
+      <c r="R86" t="n">
+        <v>330</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>1011248917</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1011248917</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>진스 핏</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>jeansfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0507-1399-8039</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 84 4층</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jeans_fit77?igsh=cXg0ZTZ0N203emlt</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P87" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2</v>
+      </c>
+      <c r="R87" t="n">
+        <v>43</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>2036358510</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2036358510</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>크런치핏</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>crunchfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1369-2362</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경원대로 863 서해빌딩 5층</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/crunchfit</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>5</v>
+      </c>
+      <c r="R88" t="n">
+        <v>13</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>1258852561</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1258852561</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>모두짐 재활PT 인천도화점</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>modoo2206@naver.com</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0507-1484-5789</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 숙골로87번길 28-1 다온1프라자 5층 모두짐 인천도화점</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@mutongweight</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P89" t="n">
+        <v>238</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>323</v>
+      </c>
+      <c r="R89" t="n">
+        <v>561</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>1514606541</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1514606541</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>뉴케이와이피트니스</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>5830666@naver.com</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0505-720-1633</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 미추홀대로 510 지하1층</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>2090228880</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2090228880</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>뉴바디짐</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>godanhe@naver.com</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>032-710-1633</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로317번길 23 해성프라자 6층 뉴바디짐</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>http://pf.kakao.com/_yyvMxb/chat</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P91" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>31</v>
+      </c>
+      <c r="R91" t="n">
+        <v>109</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>1357445067</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1357445067</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>라이프 P.T</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>mkj1104@naver.com</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0507-1366-6002</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 221 101동 214호</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>2087474006</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2087474006</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>루트짐 주안점</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>rlawnsgh3347@naver.com</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0507-1492-1172</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 석정로375번길 11 2층 루트짐 주안점</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/rlawnsgh3347</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P93" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>72</v>
+      </c>
+      <c r="R93" t="n">
+        <v>132</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>1765729791</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1765729791</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>어게인핏 PT 주안점</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>yeoninmo@naver.com</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0507-1394-8036</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 구월로40번길 4 2층 어게인핏</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/again_fit_juan?igsh=cGJremczeG83cTA%3D&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P94" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>125</v>
+      </c>
+      <c r="R94" t="n">
+        <v>197</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>1470836324</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1470836324</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>와이짐휘트니스 신기촌점</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>successful09@naver.com</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1370-9607</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인하로 304-1 지하1층</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/successful09</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P95" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>165</v>
+      </c>
+      <c r="R95" t="n">
+        <v>195</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>1390976602</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1390976602</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>유코치의슬림해짐</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>syhs007@naver.com</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0507-1465-4459</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 제일로 31 상가 2층 205호</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yoocoach007</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P96" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>30</v>
+      </c>
+      <c r="R96" t="n">
+        <v>46</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>1250104868</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1250104868</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>바름핏 PT&amp;필라테스 본점</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>brfpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>0507-1455-8691</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 소성로 150 2층바름핏</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4yrsh</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P97" t="n">
+        <v>287</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>376</v>
+      </c>
+      <c r="R97" t="n">
+        <v>663</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>1493566392</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1493566392</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>베럴핏 용현점</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>betterfitpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>0507-1401-5990</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 매소홀로 63 대신프라자 702호 베럴핏</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4a3h4</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P98" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>174</v>
+      </c>
+      <c r="R98" t="n">
+        <v>254</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>37890204</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37890204</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>레몬짐 용현점</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>lafcompany_@naver.com</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0507-1373-2249</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로 311 비젼프라자 11층 레몬짐 용현점</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>http://www.lemongym.co.kr</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4nqiq</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P99" t="n">
+        <v>362</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>11</v>
+      </c>
+      <c r="R99" t="n">
+        <v>373</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>1984607952</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1984607952</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>클럽사이클 인하대역 본점</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>clubcycle_inha@naver.com</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0507-1396-1335</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로 311 1102호</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://clubcycle.co.kr/</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5uojl</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P100" t="n">
+        <v>293</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>126</v>
+      </c>
+      <c r="R100" t="n">
+        <v>419</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>1405261682</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1405261682</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>프레임짐</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>framegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>032-423-6682</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경인로 372 201동 2층 2105호,2106호(주안동, 포레나 미추홀)</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hint</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P101" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>62</v>
+      </c>
+      <c r="R101" t="n">
+        <v>108</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>1519782630</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1519782630</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>바름핏 pt&amp;필라테스 주안점</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>brfpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>0507-1490-4455</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 인주대로 370 7층</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P102" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>137</v>
+      </c>
+      <c r="R102" t="n">
+        <v>193</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>1623977840</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1623977840</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>저스트PT짐</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>rlaehgus1236@naver.com</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0507-1379-2006</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 독배로317번길 29 11층</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4sy7u</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P103" t="n">
+        <v>119</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>209</v>
+      </c>
+      <c r="R103" t="n">
+        <v>328</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>1324594280</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1324594280</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>유리,창호공사</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>스피드부스</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>juliday@naver.com</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 아암대로 101</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>http://www.speedbooth.co.kr</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P104" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1</v>
+      </c>
+      <c r="R104" t="n">
+        <v>4</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>21799895</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21799895</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>중개업</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>뉴인천부동산공인중개사사무소</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>kittymuscle@naver.com</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 경원대로 812-1 뉴인천부동산건물2층</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/sports8948</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1</v>
+      </c>
+      <c r="R105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>1761152160</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1761152160</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>흐름필라테스&amp;요가</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>hrmpilayoga@naver.com</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0507-1470-8448</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>인천광역시 미추홀구 송림로 251 창조프라자 4층</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hrmpilayoga</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>89</v>
+      </c>
+      <c r="R106" t="n">
+        <v>310</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>1316056634</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1316056634</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/미추홀구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/미추홀구_헬스장.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -624,10 +624,10 @@
         <v>1728</v>
       </c>
       <c r="Q2" t="n">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="R2" t="n">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -658,34 +658,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>웨이빗 피트니스 24시 헬스 PT 주안점</t>
+          <t>인싸짐 주안점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>weibit@naver.com</t>
+          <t>inssagym3@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1328-8048</t>
+          <t>0507-1332-3818</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 미추홀대로 716 6층 웨이빗 피트니스</t>
+          <t>인천광역시 미추홀구 경원대로 848 지하2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/weibit_official</t>
+          <t>https://m.booking.naver.com/booking/5/bizes/840698?area=pll&amp;service-target=map-pc&amp;theme=place</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2917</v>
+        <v>1594</v>
       </c>
       <c r="Q3" t="n">
-        <v>782</v>
+        <v>1232</v>
       </c>
       <c r="R3" t="n">
-        <v>3699</v>
+        <v>2826</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1700131075</t>
+          <t>1070990223</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1700131075</t>
+          <t>https://m.place.naver.com/place/1070990223</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -752,34 +752,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>인싸짐 주안점</t>
+          <t>웨이빗 피트니스 24시 헬스 PT 주안점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>inssagym3@naver.com</t>
+          <t>weibit@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1332-3818</t>
+          <t>0507-1328-8048</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경원대로 848 지하2층</t>
+          <t>인천광역시 미추홀구 미추홀대로 716 6층 웨이빗 피트니스</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/5/bizes/840698?area=pll&amp;service-target=map-pc&amp;theme=place</t>
+          <t>https://www.instagram.com/weibit_official</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1592</v>
+        <v>2917</v>
       </c>
       <c r="Q4" t="n">
-        <v>1231</v>
+        <v>783</v>
       </c>
       <c r="R4" t="n">
-        <v>2823</v>
+        <v>3700</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1070990223</t>
+          <t>1700131075</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1070990223</t>
+          <t>https://m.place.naver.com/place/1700131075</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>플렉스짐</t>
+          <t>피트니스 연구소 인하대역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>flexgym_1@naver.com</t>
+          <t>lfitness@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1441-2280</t>
+          <t>0507-1441-2226</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 392 경인상가 3층</t>
+          <t>인천광역시 미추홀구 독배로 309 노블레스타워 8층 피트니스 연구소 인하대역점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/flexgym_1</t>
+          <t>http://www.fitnessinstitute.co.kr/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>670</v>
+        <v>2793</v>
       </c>
       <c r="Q5" t="n">
-        <v>236</v>
+        <v>378</v>
       </c>
       <c r="R5" t="n">
-        <v>906</v>
+        <v>3171</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13309652</t>
+          <t>1562966214</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13309652</t>
+          <t>https://m.place.naver.com/place/1562966214</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -940,34 +940,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피트니스 연구소 인하대역점</t>
+          <t>플렉스짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lfitness@naver.com</t>
+          <t>flexgym_1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1441-2226</t>
+          <t>0507-1441-2280</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 309 노블레스타워 8층 피트니스 연구소 인하대역점</t>
+          <t>인천광역시 미추홀구 경인로 392 경인상가 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://www.fitnessinstitute.co.kr/</t>
+          <t>https://blog.naver.com/flexgym_1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2782</v>
+        <v>670</v>
       </c>
       <c r="Q6" t="n">
-        <v>377</v>
+        <v>236</v>
       </c>
       <c r="R6" t="n">
-        <v>3159</v>
+        <v>906</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1562966214</t>
+          <t>13309652</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1562966214</t>
+          <t>https://m.place.naver.com/place/13309652</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>워라블짐 헬스 PT 도화점</t>
+          <t>짐토스24시 주안점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>wlb1203@naver.com</t>
+          <t>gymtos_juan@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1405-1273</t>
+          <t>0507-1349-8372</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 경인로 251 3층 워라블짐</t>
+          <t>인천 미추홀구 인하로 177 5, 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wlb1203</t>
+          <t>https://blog.naver.com/gymtos_juan</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1076,10 +1076,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w95x78p</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="Q7" t="n">
-        <v>235</v>
+        <v>43</v>
       </c>
       <c r="R7" t="n">
-        <v>385</v>
+        <v>223</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1596200279</t>
+          <t>2067646367</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1596200279</t>
+          <t>https://m.place.naver.com/place/2067646367</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1132,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>인싸짐 학익점 헬스 PT</t>
+          <t>올피플 24시 헬스 PT 주안 구월점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>inssagym2@naver.com</t>
+          <t>allpeople_juan@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0507-1333-3818</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 매소홀로 474 4층, 5층</t>
+          <t>인천 미추홀구 경원대로 768 7층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/12/bizes/819286/items/4778701?preview=1</t>
+          <t>http://pf.kakao.com/_bHxown</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,15 +1165,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wt9iqo1</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1185,13 +1189,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1349</v>
+        <v>446</v>
       </c>
       <c r="Q8" t="n">
-        <v>1980</v>
+        <v>656</v>
       </c>
       <c r="R8" t="n">
-        <v>3329</v>
+        <v>1102</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1204,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1303371206</t>
+          <t>2061644044</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303371206</t>
+          <t>https://m.place.naver.com/place/2061644044</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1226,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>라이노짐 인천도화점</t>
+          <t>포텐휘트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>smhon833@naver.com</t>
+          <t>jyj09623@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1349-3268</t>
+          <t>0507-1336-2892</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 송림로 249 새마을금고 3층</t>
+          <t>인천광역시 미추홀구 토금중로 13 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/smhon833</t>
+          <t>https://linktr.ee/fitness410</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1283,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="Q9" t="n">
-        <v>86</v>
+        <v>162</v>
       </c>
       <c r="R9" t="n">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1298,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1098224618</t>
+          <t>1932083996</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1098224618</t>
+          <t>https://m.place.naver.com/place/1932083996</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1337,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 미추홀구 독배로 311 1102호</t>
+          <t>인천 미추홀구 독배로 311 1102호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1358,10 +1362,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5uojl</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>O</t>
@@ -1373,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q10" t="n">
         <v>126</v>
       </c>
       <c r="R10" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1398,7 +1406,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1504,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
